--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5989,6 +5989,791 @@
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129231864</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>592153</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6401114</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129231657</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>592180</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6401008</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På flera träd i området , mkt hänglavar!</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129231719</v>
+      </c>
+      <c r="B50" t="n">
+        <v>96255</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>592153</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6401114</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129231700</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92857</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>592134</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6401093</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129231678</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90908</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>592136</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6401018</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129231796</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92161</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>592153</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6401114</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129231766</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>592153</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6401114</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6774,6 +6774,977 @@
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129248958</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98667</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>592386</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6401413</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129248837</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92862</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>592283</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6401171</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129248873</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92862</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>592350</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6401258</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129248864</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92862</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>592338</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6401232</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129249026</v>
+      </c>
+      <c r="B59" t="n">
+        <v>96263</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>592330</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6401362</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129249052</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>592341</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6401362</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129248919</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57719</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>592390</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6401237</v>
+      </c>
+      <c r="S61" t="n">
+        <v>50</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129248967</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92862</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>592386</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6401413</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129248850</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92862</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>592337</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6401262</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5994,7 +5994,7 @@
         <v>129231864</v>
       </c>
       <c r="B48" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>129231657</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>129231766</v>
       </c>
       <c r="B54" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,46 +6776,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129248958</v>
+        <v>129248873</v>
       </c>
       <c r="B55" t="n">
-        <v>98667</v>
+        <v>92864</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6823,10 +6822,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592386</v>
+        <v>592350</v>
       </c>
       <c r="R55" t="n">
-        <v>6401413</v>
+        <v>6401258</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6889,7 +6888,7 @@
         <v>129248837</v>
       </c>
       <c r="B56" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6995,45 +6994,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129248873</v>
+        <v>129248958</v>
       </c>
       <c r="B57" t="n">
-        <v>92862</v>
+        <v>98669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592350</v>
+        <v>592386</v>
       </c>
       <c r="R57" t="n">
-        <v>6401258</v>
+        <v>6401413</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96263</v>
+        <v>96265</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>129248967</v>
       </c>
       <c r="B62" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7744,6 +7744,112 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129279130</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>A 55017, Hörtingrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>592239</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6401005</v>
+      </c>
+      <c r="S64" t="n">
+        <v>75</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>I samma område som tidigare</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92168</v>
+        <v>92175</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,45 +6776,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129248873</v>
+        <v>129248958</v>
       </c>
       <c r="B55" t="n">
-        <v>92864</v>
+        <v>98676</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6822,10 +6823,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592350</v>
+        <v>592386</v>
       </c>
       <c r="R55" t="n">
-        <v>6401258</v>
+        <v>6401413</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6885,10 +6886,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129248837</v>
+        <v>129248873</v>
       </c>
       <c r="B56" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6915,7 +6916,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6931,10 +6932,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592283</v>
+        <v>592350</v>
       </c>
       <c r="R56" t="n">
-        <v>6401171</v>
+        <v>6401258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6994,46 +6995,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129248958</v>
+        <v>129248837</v>
       </c>
       <c r="B57" t="n">
-        <v>98669</v>
+        <v>92871</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592386</v>
+        <v>592283</v>
       </c>
       <c r="R57" t="n">
-        <v>6401413</v>
+        <v>6401171</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>129248967</v>
       </c>
       <c r="B62" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -5994,7 +5994,7 @@
         <v>129231864</v>
       </c>
       <c r="B48" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>129231657</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92175</v>
+        <v>92177</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>129231766</v>
       </c>
       <c r="B54" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6776,46 +6776,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129248958</v>
+        <v>129248873</v>
       </c>
       <c r="B55" t="n">
-        <v>98676</v>
+        <v>92873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6823,10 +6822,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592386</v>
+        <v>592350</v>
       </c>
       <c r="R55" t="n">
-        <v>6401413</v>
+        <v>6401258</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6886,10 +6885,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129248873</v>
+        <v>129248837</v>
       </c>
       <c r="B56" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6916,7 +6915,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6932,10 +6931,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592350</v>
+        <v>592283</v>
       </c>
       <c r="R56" t="n">
-        <v>6401258</v>
+        <v>6401171</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6995,45 +6994,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129248837</v>
+        <v>129248958</v>
       </c>
       <c r="B57" t="n">
-        <v>92871</v>
+        <v>98678</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592283</v>
+        <v>592386</v>
       </c>
       <c r="R57" t="n">
-        <v>6401171</v>
+        <v>6401413</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>129249052</v>
       </c>
       <c r="B60" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129248919</v>
+        <v>129248967</v>
       </c>
       <c r="B61" t="n">
-        <v>57719</v>
+        <v>92873</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102977</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7457,9 +7457,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7467,13 +7470,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>592390</v>
+        <v>592386</v>
       </c>
       <c r="R61" t="n">
-        <v>6401237</v>
+        <v>6401413</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7511,6 +7514,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7529,32 +7533,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129248967</v>
+        <v>129248919</v>
       </c>
       <c r="B62" t="n">
-        <v>92871</v>
+        <v>57721</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>102977</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7562,12 +7566,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7575,13 +7576,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>592386</v>
+        <v>592390</v>
       </c>
       <c r="R62" t="n">
-        <v>6401413</v>
+        <v>6401237</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7619,7 +7620,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>129279130</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>129248873</v>
       </c>
       <c r="B55" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>129248837</v>
       </c>
       <c r="B56" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>129248958</v>
       </c>
       <c r="B57" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>129248967</v>
       </c>
       <c r="B61" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7851,6 +7851,1092 @@
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129385154</v>
+      </c>
+      <c r="B65" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Skåne, Skåne, Sm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>592158</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6401256</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129383256</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Skåne, Skåne, Sm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>592216</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6400974</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129392713</v>
+      </c>
+      <c r="B67" t="n">
+        <v>92192</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>592269</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6401153</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129392688</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>592213</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6401268</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129392703</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91560</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>592271</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6401242</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129391724</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>592210</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6400973</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129391740</v>
+      </c>
+      <c r="B71" t="n">
+        <v>90572</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>592173</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6401023</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129392695</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>592259</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6401268</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129392669</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92859</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>592165</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6401238</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129392292</v>
+      </c>
+      <c r="B74" t="n">
+        <v>92821</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hörtingrum_1-4, Sm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>592153</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6401203</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Emil V. Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,45 +6776,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129248873</v>
+        <v>129248958</v>
       </c>
       <c r="B55" t="n">
-        <v>92859</v>
+        <v>98705</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6822,10 +6823,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592350</v>
+        <v>592386</v>
       </c>
       <c r="R55" t="n">
-        <v>6401258</v>
+        <v>6401413</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6885,10 +6886,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129248837</v>
+        <v>129248873</v>
       </c>
       <c r="B56" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6915,7 +6916,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6931,10 +6932,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592283</v>
+        <v>592350</v>
       </c>
       <c r="R56" t="n">
-        <v>6401171</v>
+        <v>6401258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6994,46 +6995,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129248958</v>
+        <v>129248837</v>
       </c>
       <c r="B57" t="n">
-        <v>98704</v>
+        <v>92860</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592386</v>
+        <v>592283</v>
       </c>
       <c r="R57" t="n">
-        <v>6401413</v>
+        <v>6401171</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>129248967</v>
       </c>
       <c r="B61" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>129385154</v>
       </c>
       <c r="B65" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>129392713</v>
       </c>
       <c r="B67" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>129392688</v>
       </c>
       <c r="B68" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>129392703</v>
       </c>
       <c r="B69" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>129392669</v>
       </c>
       <c r="B73" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>129392292</v>
       </c>
       <c r="B74" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>129248958</v>
       </c>
       <c r="B55" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8067,37 +8067,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129392713</v>
+        <v>129392688</v>
       </c>
       <c r="B67" t="n">
-        <v>92193</v>
+        <v>91561</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>592269</v>
+        <v>592213</v>
       </c>
       <c r="R67" t="n">
-        <v>6401153</v>
+        <v>6401268</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8176,37 +8176,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129392688</v>
+        <v>129392713</v>
       </c>
       <c r="B68" t="n">
-        <v>91561</v>
+        <v>92193</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592213</v>
+        <v>592269</v>
       </c>
       <c r="R68" t="n">
-        <v>6401268</v>
+        <v>6401153</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6095,7 +6095,7 @@
         <v>129231657</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,46 +6776,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129248958</v>
+        <v>129248873</v>
       </c>
       <c r="B55" t="n">
-        <v>98706</v>
+        <v>92863</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6823,10 +6822,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592386</v>
+        <v>592350</v>
       </c>
       <c r="R55" t="n">
-        <v>6401413</v>
+        <v>6401258</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6886,10 +6885,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129248873</v>
+        <v>129248837</v>
       </c>
       <c r="B56" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6916,7 +6915,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6932,10 +6931,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592350</v>
+        <v>592283</v>
       </c>
       <c r="R56" t="n">
-        <v>6401258</v>
+        <v>6401171</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6995,45 +6994,46 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129248837</v>
+        <v>129248958</v>
       </c>
       <c r="B57" t="n">
-        <v>92860</v>
+        <v>98710</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592283</v>
+        <v>592386</v>
       </c>
       <c r="R57" t="n">
-        <v>6401171</v>
+        <v>6401413</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129248967</v>
+        <v>129248919</v>
       </c>
       <c r="B61" t="n">
-        <v>92860</v>
+        <v>57721</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5966</v>
+        <v>102977</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7457,12 +7457,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7470,13 +7467,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>592386</v>
+        <v>592390</v>
       </c>
       <c r="R61" t="n">
-        <v>6401413</v>
+        <v>6401237</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7514,7 +7511,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7533,32 +7529,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129248919</v>
+        <v>129248967</v>
       </c>
       <c r="B62" t="n">
-        <v>57721</v>
+        <v>92863</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>102977</v>
+        <v>5966</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7566,9 +7562,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7576,13 +7575,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>592390</v>
+        <v>592386</v>
       </c>
       <c r="R62" t="n">
-        <v>6401237</v>
+        <v>6401413</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7620,6 +7619,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>129279130</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>129385154</v>
       </c>
       <c r="B65" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>129383256</v>
       </c>
       <c r="B66" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>129392688</v>
       </c>
       <c r="B67" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>129392713</v>
       </c>
       <c r="B68" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>129392703</v>
       </c>
       <c r="B69" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>129391724</v>
       </c>
       <c r="B70" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>129391740</v>
       </c>
       <c r="B71" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>129392669</v>
       </c>
       <c r="B73" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>129392292</v>
       </c>
       <c r="B74" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -7853,10 +7853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129385154</v>
+        <v>129383256</v>
       </c>
       <c r="B65" t="n">
-        <v>91564</v>
+        <v>91543</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7864,21 +7864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>592158</v>
+        <v>592216</v>
       </c>
       <c r="R65" t="n">
-        <v>6401256</v>
+        <v>6400974</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129383256</v>
+        <v>129385154</v>
       </c>
       <c r="B66" t="n">
-        <v>91543</v>
+        <v>91564</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7971,21 +7971,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>592216</v>
+        <v>592158</v>
       </c>
       <c r="R66" t="n">
-        <v>6400974</v>
+        <v>6401256</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6095,7 +6095,7 @@
         <v>129231657</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>129248873</v>
       </c>
       <c r="B55" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>129248837</v>
       </c>
       <c r="B56" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>129248958</v>
       </c>
       <c r="B57" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>129248967</v>
       </c>
       <c r="B62" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>129279130</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129383256</v>
+        <v>129385154</v>
       </c>
       <c r="B65" t="n">
-        <v>91543</v>
+        <v>91566</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7864,21 +7864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>592216</v>
+        <v>592158</v>
       </c>
       <c r="R65" t="n">
-        <v>6400974</v>
+        <v>6401256</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129385154</v>
+        <v>129383256</v>
       </c>
       <c r="B66" t="n">
-        <v>91564</v>
+        <v>91545</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7971,21 +7971,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>592158</v>
+        <v>592216</v>
       </c>
       <c r="R66" t="n">
-        <v>6401256</v>
+        <v>6400974</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8067,37 +8067,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129392688</v>
+        <v>129392713</v>
       </c>
       <c r="B67" t="n">
-        <v>91564</v>
+        <v>92198</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>592213</v>
+        <v>592269</v>
       </c>
       <c r="R67" t="n">
-        <v>6401268</v>
+        <v>6401153</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8176,37 +8176,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129392713</v>
+        <v>129392688</v>
       </c>
       <c r="B68" t="n">
-        <v>92196</v>
+        <v>91566</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592269</v>
+        <v>592213</v>
       </c>
       <c r="R68" t="n">
-        <v>6401153</v>
+        <v>6401268</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8288,7 +8288,7 @@
         <v>129392703</v>
       </c>
       <c r="B69" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>129391724</v>
       </c>
       <c r="B70" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>129391740</v>
       </c>
       <c r="B71" t="n">
-        <v>90575</v>
+        <v>90577</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>129392669</v>
       </c>
       <c r="B73" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>129392292</v>
       </c>
       <c r="B74" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90927</v>
+        <v>90931</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>129248873</v>
       </c>
       <c r="B55" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>129248837</v>
       </c>
       <c r="B56" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>129248958</v>
       </c>
       <c r="B57" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7424,32 +7424,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129248919</v>
+        <v>129248967</v>
       </c>
       <c r="B61" t="n">
-        <v>57721</v>
+        <v>92869</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>102977</v>
+        <v>5966</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7457,9 +7457,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7467,13 +7470,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>592390</v>
+        <v>592386</v>
       </c>
       <c r="R61" t="n">
-        <v>6401237</v>
+        <v>6401413</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7511,6 +7514,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7529,32 +7533,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129248967</v>
+        <v>129248919</v>
       </c>
       <c r="B62" t="n">
-        <v>92865</v>
+        <v>57721</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5966</v>
+        <v>102977</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -7562,12 +7566,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7575,13 +7576,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>592386</v>
+        <v>592390</v>
       </c>
       <c r="R62" t="n">
-        <v>6401413</v>
+        <v>6401237</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7619,7 +7620,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7853,10 +7853,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129385154</v>
+        <v>129383256</v>
       </c>
       <c r="B65" t="n">
-        <v>91566</v>
+        <v>91549</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7864,21 +7864,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7888,10 +7888,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>592158</v>
+        <v>592216</v>
       </c>
       <c r="R65" t="n">
-        <v>6401256</v>
+        <v>6400974</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7960,10 +7960,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129383256</v>
+        <v>129385154</v>
       </c>
       <c r="B66" t="n">
-        <v>91545</v>
+        <v>91570</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7971,21 +7971,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7995,10 +7995,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>592216</v>
+        <v>592158</v>
       </c>
       <c r="R66" t="n">
-        <v>6400974</v>
+        <v>6401256</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8067,37 +8067,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129392713</v>
+        <v>129392688</v>
       </c>
       <c r="B67" t="n">
-        <v>92198</v>
+        <v>91570</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8113,10 +8113,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>592269</v>
+        <v>592213</v>
       </c>
       <c r="R67" t="n">
-        <v>6401153</v>
+        <v>6401268</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8176,37 +8176,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129392688</v>
+        <v>129392713</v>
       </c>
       <c r="B68" t="n">
-        <v>91566</v>
+        <v>92202</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8222,10 +8222,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592213</v>
+        <v>592269</v>
       </c>
       <c r="R68" t="n">
-        <v>6401268</v>
+        <v>6401153</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8288,7 +8288,7 @@
         <v>129392703</v>
       </c>
       <c r="B69" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>129391724</v>
       </c>
       <c r="B70" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>129391740</v>
       </c>
       <c r="B71" t="n">
-        <v>90577</v>
+        <v>90581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>129392669</v>
       </c>
       <c r="B73" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>129392292</v>
       </c>
       <c r="B74" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 55017-2021 artfynd.xlsx
+++ b/artfynd/A 55017-2021 artfynd.xlsx
@@ -6211,7 +6211,7 @@
         <v>129231719</v>
       </c>
       <c r="B50" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>129231700</v>
       </c>
       <c r="B51" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>129231678</v>
       </c>
       <c r="B52" t="n">
-        <v>90931</v>
+        <v>90932</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>129231796</v>
       </c>
       <c r="B53" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6776,45 +6776,46 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129248873</v>
+        <v>129248958</v>
       </c>
       <c r="B55" t="n">
-        <v>92869</v>
+        <v>98724</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6822,10 +6823,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592350</v>
+        <v>592386</v>
       </c>
       <c r="R55" t="n">
-        <v>6401258</v>
+        <v>6401413</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6885,10 +6886,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129248837</v>
+        <v>129248873</v>
       </c>
       <c r="B56" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6915,7 +6916,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6931,10 +6932,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>592283</v>
+        <v>592350</v>
       </c>
       <c r="R56" t="n">
-        <v>6401171</v>
+        <v>6401258</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6994,46 +6995,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129248958</v>
+        <v>129248837</v>
       </c>
       <c r="B57" t="n">
-        <v>98716</v>
+        <v>92870</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7041,10 +7041,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592386</v>
+        <v>592283</v>
       </c>
       <c r="R57" t="n">
-        <v>6401413</v>
+        <v>6401171</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7107,7 +7107,7 @@
         <v>129248864</v>
       </c>
       <c r="B58" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>129249026</v>
       </c>
       <c r="B59" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>129248967</v>
       </c>
       <c r="B61" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129248850</v>
       </c>
       <c r="B63" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>129383256</v>
       </c>
       <c r="B65" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>129385154</v>
       </c>
       <c r="B66" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>129392688</v>
       </c>
       <c r="B67" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>129392713</v>
       </c>
       <c r="B68" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>129392703</v>
       </c>
       <c r="B69" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>129391724</v>
       </c>
       <c r="B70" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>129391740</v>
       </c>
       <c r="B71" t="n">
-        <v>90581</v>
+        <v>90582</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>129392669</v>
       </c>
       <c r="B73" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>129392292</v>
       </c>
       <c r="B74" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
